--- a/car_plate_no.xlsx
+++ b/car_plate_no.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomrho/Desktop/EXE/ML/yolov10/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{307C20B9-83B2-7849-B733-5D1B8C43FDE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D6FE8C-7B0E-264B-A917-01D38EE91DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="2200" windowWidth="28040" windowHeight="17440" xr2:uid="{F599A074-5C00-AB4C-8C79-58C778A87748}"/>
+    <workbookView xWindow="24900" yWindow="2460" windowWidth="10000" windowHeight="17440" xr2:uid="{F599A074-5C00-AB4C-8C79-58C778A87748}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>ABC123</t>
-  </si>
-  <si>
-    <t>NZ4567</t>
-  </si>
-  <si>
-    <t>XYZ789</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>EASY2C</t>
+  </si>
+  <si>
+    <t>2L84WK</t>
+  </si>
+  <si>
+    <t>FMQ668</t>
+  </si>
+  <si>
+    <t>QIK MUM</t>
+  </si>
+  <si>
+    <t>PONSNB</t>
+  </si>
+  <si>
+    <t>GRT NAN</t>
+  </si>
+  <si>
+    <t>RVEGAS</t>
+  </si>
+  <si>
+    <t>IWDD8U</t>
+  </si>
+  <si>
+    <t>M4RYME</t>
   </si>
 </sst>
 </file>
@@ -416,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C589A462-024B-1F4D-B38E-8898A177F2A9}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -426,12 +444,42 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
